--- a/www/download/IND.hours_worked.empe_hs.r.pc.rpA2.xlsx
+++ b/www/download/IND.hours_worked.empe_hs.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>0.289179392521891</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>0.299895186331886</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>0.31064526404066</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>0.321451997308945</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>0.332336543058694</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>0.343319270535466</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>0.354420114520615</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>0.362630749585223</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>0.368036836719538</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>0.360309100435381</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>0.353973775800604</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>0.353973775800604</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>0.353973775800604</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>0.353973775800604</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>0.353973775800604</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>0.24827785766696</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>0.248210279362874</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>0.247157476528456</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>0.251086953099824</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>0.29511143736356</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>0.300571539916673</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0.30038634003246</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>0.307618761773745</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>0.307482790631396</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>0.360974374933702</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349246310726459</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>0.345217867279827</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>0.350986805170642</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>0.341453627923499</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>0.359314744130337</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>0.295356757269898</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.300043830085986</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>0.30387931680274</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>0.306243799212082</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>0.3076386966893</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>0.307638918727479</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>0.309575133915821</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>0.31115236386445</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>0.31149309581594</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>0.32095699670793</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>0.32249585075525</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>0.322806633897985</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>0.332069674114175</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>0.367327769700386</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>0.367746217778343</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>0.233175632421713</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.23253959469975</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>0.220194395322882</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.20815449878133</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>0.211434792120948</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>0.215353752477266</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>0.21580284304186</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>0.223774869612283</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.261459806563282</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>0.266378193511664</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>0.279458030492262</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>0.286412987163339</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>0.298013364501723</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318452698794842</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0.329335976037564</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.29409052632085</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>0.296079227090833</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>0.297903785160528</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>0.299578526879231</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>0.301115664348116</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>0.302525690731196</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>0.303817683651494</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>0.304999541148803</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.307662199656366</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>0.310168322533745</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.312530559686387</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>0.323703354133469</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>0.334233478808998</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>0.344188726643852</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>0.353625231082756</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>0.283887302200348</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>0.285670803300515</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>0.290353545121221</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>0.298563117887347</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>0.295937329398875</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>0.30465518606849</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>0.314558168088238</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>0.319333592254155</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324247100564213</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0.329304172845394</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>0.342471928600837</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>0.354529651891686</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>0.366693601378756</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>0.36334859640695</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>0.378855210793273</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>0.124037447713303</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>0.129220703596066</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>0.134552088242334</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0.140032048771413</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>0.145660831999268</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>0.151438479316688</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>0.157364822071122</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>0.163439477471944</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0.176850380035678</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>0.185294918774335</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>0.207592519675351</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>0.227850360110618</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>0.220328484449765</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.232492043704894</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.232492043704894</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>0.544864812173054</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.540463632985101</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528380219092659</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.45</t>
+          <t>0.514519904127518</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>0.508841283917387</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>51.66</t>
+          <t>0.516559088283292</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>0.521198697260749</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>53.08</t>
+          <t>0.530844853898839</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>53.29</t>
+          <t>0.532927240854719</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>0.524600145198247</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>0.505820885113892</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>0.504820775395999</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>0.527082119469519</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>0.534037031944217</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>54.13</t>
+          <t>0.541263308825268</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.210006915423132</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.210006915423132</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.210006915423132</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.210006915423132</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0.21393340522273</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>0.217802186320653</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>0.221398378238704</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>0.227865431976431</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0.227842367601091</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>0.239770492408704</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>0.241922347985495</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>24.86</t>
+          <t>0.248635899917477</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>0.247966233047572</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>0.258863290251484</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>0.278259581479081</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>0.393819180663955</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>0.395025210109739</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>0.39659801633945</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.41299369341765</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>0.410432331257694</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>0.410506960143121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>0.416300607079038</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>0.423331044584821</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>44.28</t>
+          <t>0.442806197211773</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>0.450157894154631</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>0.446913876649963</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>0.438678513111825</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>0.431780702172936</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>0.439531299891024</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>0.456494261196427</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>0.386812349325059</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>0.39679394129873</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>0.405783630873547</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>0.415204080436876</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>0.419883812692644</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>0.420257997596477</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>0.429898166099418</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>0.43899239834013</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>0.481020905048913</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>0.4850804102428</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>50.13</t>
+          <t>0.501317782629348</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>0.506985826067859</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>48.27</t>
+          <t>0.4826845310024</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>0.51232996429474</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>51.79</t>
+          <t>0.517862916599619</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>0.495408913309027</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.99</t>
+          <t>0.519861965374061</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>0.523874140592586</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>0.546230754694524</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557548779375976</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>0.580520710325762</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>0.591788063881119</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>60.19</t>
+          <t>0.601861001472302</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60.89</t>
+          <t>0.608931176998803</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>61.48</t>
+          <t>0.614845449027526</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>62.42</t>
+          <t>0.624183935626363</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>0.628808984805309</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>0.63271750962188</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>63.49</t>
+          <t>0.634856613137847</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>64.77</t>
+          <t>0.647689049643976</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>53.18</t>
+          <t>0.531829004552595</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.51</t>
+          <t>0.525089086452411</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>0.517666710432824</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>0.509186085967553</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>0.494162685057745</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>0.500674090550267</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>0.504438033180471</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>51.26</t>
+          <t>0.512588864937562</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503765006341259</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>0.524337237871557</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>0.543064042950419</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>0.538267789634217</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>0.538045983770225</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>0.542869209762013</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>0.554975521217162</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>0.531583752847227</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>0.537439539709237</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>53.95</t>
+          <t>0.539455854980769</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>0.53853010128221</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53.94</t>
+          <t>0.539421799787608</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>0.537722832347294</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>0.540744529792842</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>0.543536238959717</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>54.61</t>
+          <t>0.546051649350593</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>55.26</t>
+          <t>0.552573726207923</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>55.26</t>
+          <t>0.552636269675438</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>0.552844961452021</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>0.559563483715315</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>0.563989742484564</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>0.583110000839566</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>0.406507190480633</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>0.415876867079149</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424831414317406</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>0.433287818516768</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>0.446827440109192</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>0.451096858939492</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>0.458968416893304</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>0.463407126105263</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>0.466241557318442</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>0.475911067082412</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>0.492772926424855</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>0.509377410545696</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>0.51426297134454</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>52.09</t>
+          <t>0.520904897877459</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>54.32</t>
+          <t>0.543194815443563</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>0.426055835058621</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.36</t>
+          <t>0.42355353090756</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>0.437324958328552</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>0.455572437960996</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>0.472839803087316</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>0.491061196832171</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>0.500607267965176</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>0.51095058544482</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>0.50726261102816</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>0.498522322896714</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>0.50434538558141</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>0.51603369333474</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.54048769495447</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>54.04</t>
+          <t>0.540414298050232</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>0.543479078583824</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>0.371346947245537</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>0.377495351521338</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>0.380895490214712</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>0.383899325003038</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>0.366128130166343</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>37.48</t>
+          <t>0.374798240107462</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>0.371233029195161</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>0.379927010715208</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>0.384015821018181</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.401867741789303</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.397578739785172</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>0.42497703068806</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>0.434158894495118</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>0.436895912157739</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>0.438482748779813</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275519325944415</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275519325944415</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275519325944415</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275519325944415</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>0.294574012300233</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>0.282796701011719</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>0.283232330233021</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>0.285428125426209</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>0.29600256785434</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>0.319291335752203</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>0.328504310867041</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>33.29</t>
+          <t>0.332926983442173</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>0.332037142612504</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.356705171014714</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>0.359591681237133</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>0.163938581931057</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>0.174265607700166</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>0.168744998999257</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>0.187020418426581</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191358579639516</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>0.214048340035937</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>0.216384149695325</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>0.215760201118645</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>0.20520128244658</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>0.220466023267421</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22.88</t>
+          <t>0.228789349052772</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>0.236415279689342</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>23.93</t>
+          <t>0.239301121356142</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>23.93</t>
+          <t>0.239301121356142</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>23.93</t>
+          <t>0.239301121356142</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>0.296050006052734</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>0.298581576242641</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>0.300909903891421</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>0.303042993620904</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>0.304987730895305</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>0.321843902982895</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>0.337829004818183</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>0.353024276833417</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>0.367499841489644</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381316634576217</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381316634576217</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381316634576217</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381316634576217</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381316634576217</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381316634576217</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>0.41132230650555</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.427637073771549</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>0.429194920010672</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>0.445920525466983</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>0.460949134456281</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>0.468503566272838</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>0.479260270875987</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>0.500930943286282</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>0.524329133556936</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>0.549304944270521</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>55.62</t>
+          <t>0.556246259500836</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>0.573232942758362</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>0.586308994149082</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>0.602086237445446</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>0.627644332434433</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>0.192904605624275</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>0.200113075185827</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>0.20758879667445</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>0.214562578033492</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>0.228392612827319</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>0.229868284167139</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>0.239162143213746</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>0.248423464470472</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>0.257216912637063</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0.239965130230706</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262704438874699</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>0.278571249243567</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>0.28967845123482</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>0.314434245991452</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>0.305133464974963</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>0.355259208929566</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>0.362489266994182</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.82</t>
+          <t>0.368229777671674</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>0.378964815710906</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>0.387284294641542</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>0.392477077482147</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>0.403755074305688</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>0.415452544482424</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>0.416934961034728</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>0.419814950813904</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418894617770864</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418894617770864</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418894617770864</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418894617770864</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418894617770864</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>0.489511680585409</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>0.508532507725583</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>0.517086939922077</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>0.545792790757592</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>0.557686035995283</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>55.47</t>
+          <t>0.554722509637637</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>0.568996143776992</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>60.27</t>
+          <t>0.602663536711298</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0.609998511951371</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>61.52</t>
+          <t>0.615204636156917</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626509537129112</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626509537129112</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626509537129112</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626509537129112</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626509537129112</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>0.465057971336289</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>0.458407948288268</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>0.450844210371361</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>0.442417743916483</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>0.428675170993141</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>0.432678626367677</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435437582968223</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>0.443663284304168</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>0.465270116015049</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>0.464322489564079</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>0.478724732434004</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>0.482193462315508</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>0.502041307075269</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>51.14</t>
+          <t>0.511366793939143</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.526037135464151</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.440449953373005</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0.407498090282461</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>0.390152071306385</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>0.373546159227996</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>0.358509866649535</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>0.35984720599384</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>36.12</t>
+          <t>0.361227610574591</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>0.36412240445629</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>0.282458084040545</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>0.423231943366635</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>0.445676619527215</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>0.401250131112525</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>0.430535177479287</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>0.417261599026023</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>50.64</t>
+          <t>0.506364739546676</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>0.41586310750685</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>0.409419154851023</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>0.401209300670639</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>0.392388904734825</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>0.380191106523993</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>0.384681369127382</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>0.387341608883431</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.39471247671173</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>0.368854459968821</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>0.401240465581585</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>0.3776595721595</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>0.388072468405076</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>0.415639152203064</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>0.457172042496231</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>0.451439339675188</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>0.375109989595781</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0.370016814001778</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>0.363162905601156</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>0.364837036815617</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>0.363071019184611</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>0.36570754369466</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>0.363457203239857</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>0.361462698478045</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>0.359835656752129</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>0.357057176874857</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>0.35534965877495</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>0.346988574347895</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>0.346988574347895</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>0.346988574347895</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>0.346988574347895</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>0.233175632421713</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.23253959469975</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>0.220194395322882</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.20815449878133</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>0.211434792120948</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>0.215353752477266</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>0.21580284304186</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>0.223774869612283</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.261459806563282</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>0.266378193511664</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>0.279458030492262</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>0.286412987163339</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>0.298013364501723</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318452698794842</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0.329335976037564</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>0.340084943349773</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.362775596300016</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>0.394261979441324</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>0.38874187067136</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>0.426763256872053</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>40.76</t>
+          <t>0.407619295160398</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>0.397267530472071</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>0.423763681833521</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>0.462620058503322</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>0.488968617551751</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>0.494122167143002</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>0.490953451423454</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>0.488476187756936</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>0.505706884861041</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>0.513632455190847</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245560109621577</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245560109621577</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245560109621577</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245560109621577</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245560109621577</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245560109621577</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>0.265472914298966</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>0.280188938276081</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>0.305522940440345</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>0.337092962442832</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>0.351700519327732</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>0.361631061331169</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>0.368252691901072</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>0.37426401807909</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>0.398389880096646</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>0.233175632421713</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.23253959469975</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>0.220194395322882</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.20815449878133</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>0.211434792120948</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>0.215353752477266</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>0.21580284304186</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>0.223774869612283</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.261459806563282</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>0.266378193511664</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>0.279458030492262</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>0.286412987163339</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>0.298013364501723</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318452698794842</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0.329335976037564</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>0.233175632421713</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.23253959469975</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>0.220194395322882</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.20815449878133</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>0.211434792120948</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>0.215353752477266</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>0.21580284304186</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>0.223774869612283</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.261459806563282</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>0.266378193511664</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>0.279458030492262</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>0.286412987163339</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>0.298013364501723</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318452698794842</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0.329335976037564</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199638133914174</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199638133914174</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199638133914174</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199638133914174</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>0.203700910428263</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>0.207532733418375</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>0.211021880881032</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>0.217531168200856</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>0.221960320043293</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>0.225366037027816</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.229008655252518</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.229008655252518</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.229008655252518</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.229008655252518</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.229008655252518</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226144594113496</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226144594113496</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226144594113496</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226144594113496</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>0.213206625326704</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>0.214454339777001</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>0.220203042021981</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.218411694925504</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>0.229916873864405</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>0.237779363675329</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>0.260223879229841</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>0.27029459181042</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>0.269389586538394</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>0.270430175752889</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>0.282259393564082</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>0.29767061222955</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>0.29767061222955</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>0.29767061222955</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>0.29767061222955</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.307668897508627</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>0.326605282690006</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>27.41</t>
+          <t>0.274140714955531</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>0.303511778976121</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>0.336187638665282</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>0.352645588588238</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>0.361457514461163</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>37.48</t>
+          <t>0.374785132924547</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>0.380563311562413</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>0.395559408618554</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>0.418147249194264</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>0.28483906005986</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>0.287373374823972</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>0.293555082319156</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>0.298545897251331</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>0.313840724744835</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>0.340168230617697</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>0.350500995584561</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>0.359416621111238</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>0.363874227389124</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>0.375984919931042</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>0.394208050438851</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>0.411549684612957</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>0.417460150610919</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>0.436912596125648</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>0.458407403898322</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>0.272167840665116</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>0.28320343665693</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>0.305090778471066</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>0.290544861609576</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>0.312232633418881</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>0.317844774456991</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>0.330354133119758</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>0.343958491529621</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>0.360997355349063</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>0.335880669962547</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>0.350572839672933</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>36.23</t>
+          <t>0.362257207982644</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>0.370216993729715</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>0.376456161963932</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>0.382515149334895</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>46.58</t>
+          <t>0.46578339419153</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.47411886796269</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>0.481789249005576</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>0.488836328821002</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>49.53</t>
+          <t>0.495294945759837</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50.12</t>
+          <t>0.501193933837463</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50.66</t>
+          <t>0.506556822958362</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>51.14</t>
+          <t>0.511402344830883</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>0.5182831640913</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>52.48</t>
+          <t>0.524844111866623</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>0.535401636979529</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>55.19</t>
+          <t>0.55188916581959</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>0.552210714567552</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>0.567566090418859</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>0.594553860897891</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>0.414075250524946</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>0.413238752388813</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>0.416583171486772</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>0.423052783576711</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424751474484819</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.427653072469849</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>0.435575195878394</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>43.98</t>
+          <t>0.439834309884847</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>0.433232837075673</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>0.44628808354747</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>0.449205122214138</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>0.453646319351127</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>0.453651749318137</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>0.459440576178621</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>0.469778038443654</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>0.35888876847864</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>0.361768228723269</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>0.363434604258784</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>0.366239830682011</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>0.37078657430088</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>0.375910369161607</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>0.380326360659847</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>0.389706676967636</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>0.397351885995968</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0.41009703203073</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>0.417337188241025</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>0.422705102041738</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>0.428799573585419</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>0.438082000527252</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>0.449929453161122</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>33.54</t>
+          <t>0.335405028268111</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>0.338411136515854</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0.339669704236783</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>34.19</t>
+          <t>0.341902289518561</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>0.346903533136329</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>0.352299549381363</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>0.356278330181676</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>0.365145077653606</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>0.373805487600321</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>0.386008543030156</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>0.393178355201567</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398494066586867</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>0.40454560307515</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>0.414310993611769</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>0.425707442136482</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
